--- a/TFG_FASE_1/02_datasets/metadata/RESULTADOS FASE 0.xlsx
+++ b/TFG_FASE_1/02_datasets/metadata/RESULTADOS FASE 0.xlsx
@@ -25673,7 +25673,7 @@
       <c r="U25" s="81"/>
       <c r="V25" s="82"/>
     </row>
-    <row r="26" s="87" customFormat="true" ht="42.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" s="87" customFormat="true" ht="72.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="83" t="s">
         <v>25</v>
       </c>
